--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536319_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536319_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.3869</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8836000000000001</v>
+        <v>2.0704</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1.6835</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8836000000000001</v>
+        <v>-1.3287</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2918</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5918</v>
+        <v>-1.2602</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8836000000000001</v>
+        <v>1.633</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2918</v>
+        <v>1.9452</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5918</v>
+        <v>-0.3122</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-2.9617</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-2.0137</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.948</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.8493</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.5444</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.2576</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3493</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8288</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>S. THOMAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3869</v>
+        <v>0.1924</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0704</v>
+        <v>1.3216</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6835</v>
+        <v>-1.1292</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3287</v>
+        <v>0.9383</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2602</v>
+        <v>0.9463</v>
       </c>
       <c r="J17" t="n">
-        <v>1.633</v>
+        <v>2.2381</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9452</v>
+        <v>1.5274</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3122</v>
+        <v>0.7107</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9617</v>
+        <v>-1.2998</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0137</v>
+        <v>-1.5354</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.948</v>
+        <v>0.2356</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8219</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0274</v>
+        <v>-3.0822</v>
       </c>
       <c r="R17" t="n">
         <v>1.8493</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5444</v>
+        <v>0.7706</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2867</v>
+        <v>0.748</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2576</v>
+        <v>0.0226</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3493</v>
+        <v>-0.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1781</v>
+        <v>1.4178</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8288</v>
+        <v>-1.7014</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. THOMAS</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1924</v>
+        <v>-0.1206</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3216</v>
+        <v>1.1325</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1292</v>
+        <v>-1.2531</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9383</v>
+        <v>1.9134</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.008</v>
+        <v>1.046</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9463</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2381</v>
+        <v>1.714</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5274</v>
+        <v>1.5561</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7107</v>
+        <v>0.1578</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2998</v>
+        <v>0.1994</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5354</v>
+        <v>-0.5102</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2356</v>
+        <v>0.7096</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2329</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8493</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7706</v>
+        <v>0.0551</v>
       </c>
       <c r="T18" t="n">
-        <v>0.748</v>
+        <v>-0.2321</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0226</v>
+        <v>0.2872</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2836</v>
+        <v>-2.7055</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4178</v>
+        <v>-0.3493</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7014</v>
+        <v>-2.3561</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1206</v>
+        <v>-0.8875</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1325</v>
+        <v>-0.4035</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2531</v>
+        <v>-0.4841</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9134</v>
+        <v>2.1348</v>
       </c>
       <c r="H19" t="n">
-        <v>1.046</v>
+        <v>1.9523</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.1825</v>
       </c>
       <c r="J19" t="n">
-        <v>1.714</v>
+        <v>1.9042</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5561</v>
+        <v>2.1786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1578</v>
+        <v>-0.2744</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1994</v>
+        <v>0.2306</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5102</v>
+        <v>-0.2263</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7096</v>
+        <v>0.457</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.0274</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0551</v>
+        <v>-0.5333</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2321</v>
+        <v>-0.2528</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2872</v>
+        <v>-0.2805</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.7055</v>
+        <v>-1.4616</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3493</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3561</v>
+        <v>-1.4616</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>X. TORRENT BAYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8875</v>
+        <v>-0.9526</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4035</v>
+        <v>-0.1488</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4841</v>
+        <v>-0.8038</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1348</v>
+        <v>-0.8733</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9523</v>
+        <v>-0.4186</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1825</v>
+        <v>-0.4547</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9042</v>
+        <v>0.4632</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1786</v>
+        <v>1.0115</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2744</v>
+        <v>-0.5483</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2306</v>
+        <v>-1.3365</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2263</v>
+        <v>-1.4301</v>
       </c>
       <c r="O20" t="n">
-        <v>0.457</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0274</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.0548</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0274</v>
+        <v>1.8493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5333</v>
+        <v>-0.1135</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2528</v>
+        <v>0.0251</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2805</v>
+        <v>-0.1386</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4616</v>
+        <v>0.2397</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4616</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8361</v>
+        <v>-2.6888</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0323</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8038</v>
+        <v>-1.7397</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7569</v>
+        <v>0.2203</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7104</v>
+        <v>0.0389</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0464</v>
+        <v>0.1814</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4204</v>
+        <v>0.0784</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7197</v>
+        <v>0.0389</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1401</v>
+        <v>0.0395</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3365</v>
+        <v>0.1419</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4301</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1419</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2055</v>
+        <v>-0.411</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8493</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1135</v>
+        <v>-0.1419</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0251</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1386</v>
+        <v>-0.1419</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2397</v>
+        <v>-2.3561</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1781</v>
+        <v>-2.3561</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>B. SAGNA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6888</v>
+        <v>-2.9894</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-2.1445</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7397</v>
+        <v>-0.8449</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2203</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0389</v>
+        <v>-0.2997</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1814</v>
+        <v>-0.6937</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0784</v>
+        <v>0.1853</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0389</v>
+        <v>0.263</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0395</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1419</v>
+        <v>-1.1787</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.5628</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1419</v>
+        <v>-0.6159</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.411</v>
+        <v>-1.6439</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1419</v>
+        <v>0.1711</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.275</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1419</v>
+        <v>0.4461</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3561</v>
+        <v>-0.5233</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3561</v>
+        <v>-0.5233</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. SAGNA</t>
+          <t>J. LEEROY OSAGIE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9894</v>
+        <v>-3.399</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1445</v>
+        <v>-2.6435</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8449</v>
+        <v>-0.7556</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.1071</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2997</v>
+        <v>-0.9646</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6937</v>
+        <v>-0.1425</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1853</v>
+        <v>0.6502</v>
       </c>
       <c r="K24" t="n">
-        <v>0.263</v>
+        <v>-0.6123</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.07779999999999999</v>
+        <v>1.2625</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1787</v>
+        <v>-1.7573</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5628</v>
+        <v>-0.3523</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6159</v>
+        <v>-1.4049</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6439</v>
+        <v>-2.6713</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0548</v>
+        <v>-3.0822</v>
       </c>
       <c r="R24" t="n">
         <v>0.411</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1711</v>
+        <v>-0.3193</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.275</v>
+        <v>-0.2114</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4461</v>
+        <v>-0.1079</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5233</v>
+        <v>0.6986</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5233</v>
+        <v>0.6986</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. LEEROY OSAGIE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.399</v>
+        <v>-7.3657</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6435</v>
+        <v>1.739100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7556</v>
+        <v>-9.104799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1071</v>
+        <v>2.4249</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9646</v>
+        <v>0.3671999999999996</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1425</v>
+        <v>2.0578</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6502</v>
+        <v>16.0802</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6123</v>
+        <v>11.5671</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2625</v>
+        <v>4.513</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7573</v>
+        <v>-13.6555</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3523</v>
+        <v>-11.2001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4049</v>
+        <v>-2.4549</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.6713</v>
+        <v>-4.1099</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.0822</v>
+        <v>-18.4932</v>
       </c>
       <c r="R25" t="n">
-        <v>0.411</v>
+        <v>14.3835</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3193</v>
+        <v>1.7371</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2114</v>
+        <v>1.0566</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1079</v>
+        <v>0.6803</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6986</v>
+        <v>-7.4179</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.0959</v>
       </c>
       <c r="X25" t="n">
-        <v>0.6986</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536319_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SOL GIRONÈS BISBAL BÀSQUET</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-7.365599999999999</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.739199999999999</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-9.104799999999999</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.4249</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.3671999999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.0579</v>
-      </c>
-      <c r="J26" t="n">
-        <v>16.0802</v>
-      </c>
-      <c r="K26" t="n">
-        <v>11.5671</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4.513000000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-13.6555</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-11.2001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-2.4549</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-4.109900000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-18.4932</v>
-      </c>
-      <c r="R26" t="n">
-        <v>14.3835</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.7371</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.0566</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.6802999999999998</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-7.4179</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.095899999999999</v>
-      </c>
-      <c r="X26" t="n">
         <v>-10.5137</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
